--- a/data/trans_orig/DCD_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/DCD_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) en 2023</t>
+          <t>Población con dolor crónico discapacitante (incluye Otro dolor crónico) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88140</t>
+          <t>89048</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>124384</t>
+          <t>125049</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>150369</t>
+          <t>151807</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>215322</t>
+          <t>216623</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>256930</t>
+          <t>264463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>325318</t>
+          <t>327383</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>511057</t>
+          <t>510392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>547301</t>
+          <t>546393</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>510008</t>
+          <t>508707</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>574961</t>
+          <t>573523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1035454</t>
+          <t>1033389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1103842</t>
+          <t>1096309</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,57%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71834</t>
+          <t>58654</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>172201</t>
+          <t>170250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>242014</t>
+          <t>241388</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>286790</t>
+          <t>286640</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>261774</t>
+          <t>252678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>452219</t>
+          <t>452472</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1020663</t>
+          <t>1022614</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1121030</t>
+          <t>1134210</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>671861</t>
+          <t>672011</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>716637</t>
+          <t>717263</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1699297</t>
+          <t>1699044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1889742</t>
+          <t>1898838</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,26%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71070</t>
+          <t>71018</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105612</t>
+          <t>105759</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>115456</t>
+          <t>97017</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>270997</t>
+          <t>270890</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>198577</t>
+          <t>194291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>338607</t>
+          <t>342019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>599068</t>
+          <t>598921</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633610</t>
+          <t>633662</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>662369</t>
+          <t>662476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>817910</t>
+          <t>836349</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1299439</t>
+          <t>1296027</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1439469</t>
+          <t>1443755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120470</t>
+          <t>121691</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>165177</t>
+          <t>162271</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>233515</t>
+          <t>236454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>325511</t>
+          <t>326154</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>386375</t>
+          <t>383096</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>472920</t>
+          <t>470906</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>761654</t>
+          <t>764560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>806361</t>
+          <t>805140</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>769421</t>
+          <t>768778</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>861417</t>
+          <t>858478</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1548843</t>
+          <t>1550857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1635388</t>
+          <t>1638667</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,05%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>360611</t>
+          <t>364903</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>516813</t>
+          <t>519297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>772295</t>
+          <t>764091</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1028292</t>
+          <t>1028185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1227473</t>
+          <t>1213709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1521176</t>
+          <t>1516243</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2943004</t>
+          <t>2940520</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3099206</t>
+          <t>3094914</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2683988</t>
+          <t>2684095</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2939985</t>
+          <t>2948189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5650921</t>
+          <t>5655854</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5944624</t>
+          <t>5958388</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/DCD_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/DCD_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>105998</t>
+          <t>113168</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89048</t>
+          <t>95867</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125049</t>
+          <t>132690</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>192653</t>
+          <t>206837</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151807</t>
+          <t>189221</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>216623</t>
+          <t>228119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>298651</t>
+          <t>320005</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>264463</t>
+          <t>293248</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>327383</t>
+          <t>346523</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>529443</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>510392</t>
+          <t>558020</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>546393</t>
+          <t>594843</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>532677</t>
+          <t>527343</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>508707</t>
+          <t>506061</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>573523</t>
+          <t>544959</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>68,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1062121</t>
+          <t>1104884</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1033389</t>
+          <t>1078366</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1096309</t>
+          <t>1131641</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>79,42%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>127906</t>
+          <t>136471</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58654</t>
+          <t>116452</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>170250</t>
+          <t>160202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>263884</t>
+          <t>292452</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>241388</t>
+          <t>267172</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>286640</t>
+          <t>318014</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>391791</t>
+          <t>428923</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>252678</t>
+          <t>396224</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>452472</t>
+          <t>465726</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1064958</t>
+          <t>912446</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1022614</t>
+          <t>888715</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1134210</t>
+          <t>932465</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>694767</t>
+          <t>779022</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>672011</t>
+          <t>753460</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>717263</t>
+          <t>804302</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1759725</t>
+          <t>1691468</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1699044</t>
+          <t>1654665</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1898838</t>
+          <t>1724167</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>81,31%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86912</t>
+          <t>98977</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71018</t>
+          <t>81110</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105759</t>
+          <t>119287</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>201374</t>
+          <t>233528</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97017</t>
+          <t>210673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>270890</t>
+          <t>258372</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>288287</t>
+          <t>332505</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>194291</t>
+          <t>302184</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>342019</t>
+          <t>363523</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>617768</t>
+          <t>704096</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>598921</t>
+          <t>683786</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633662</t>
+          <t>721963</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>731992</t>
+          <t>578731</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>662476</t>
+          <t>553887</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>836349</t>
+          <t>601586</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1349759</t>
+          <t>1282827</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1296027</t>
+          <t>1251809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1443755</t>
+          <t>1313148</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>141763</t>
+          <t>147722</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>121691</t>
+          <t>127568</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162271</t>
+          <t>170685</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>291634</t>
+          <t>317420</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>236454</t>
+          <t>292060</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>326154</t>
+          <t>345331</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>433397</t>
+          <t>465142</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>383096</t>
+          <t>432584</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>470906</t>
+          <t>503198</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>785068</t>
+          <t>842340</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>764560</t>
+          <t>819377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>805140</t>
+          <t>862494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>803298</t>
+          <t>801621</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>768778</t>
+          <t>773710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>858478</t>
+          <t>826981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1588366</t>
+          <t>1643962</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1550857</t>
+          <t>1605906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1638667</t>
+          <t>1676520</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>462580</t>
+          <t>496338</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>364903</t>
+          <t>457883</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>519297</t>
+          <t>543216</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>949546</t>
+          <t>1050237</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>764091</t>
+          <t>1006147</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1028185</t>
+          <t>1101531</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1412125</t>
+          <t>1546575</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1213709</t>
+          <t>1477371</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1516243</t>
+          <t>1607726</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2997237</t>
+          <t>3036424</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2940520</t>
+          <t>2989546</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3094914</t>
+          <t>3074879</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2762734</t>
+          <t>2686717</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2684095</t>
+          <t>2635423</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2948189</t>
+          <t>2730807</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5759972</t>
+          <t>5723141</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5655854</t>
+          <t>5661990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5958388</t>
+          <t>5792345</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
